--- a/Final Project - Josie/Categorical_Regression_Analysis.xlsx
+++ b/Final Project - Josie/Categorical_Regression_Analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,28 +458,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FATONMEATTYPE</t>
+          <t>MILKTYPE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>Old</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>49839913.52412284</v>
+        <v>-0.721648507544728</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01080109491415556</v>
+        <v>0.0378902189982528</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SUGARINTEA</t>
+          <t>ICEDTEATYPE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -491,31 +491,73 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-53203172.51252006</v>
+        <v>-0.2214902338161595</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01853379851825863</v>
+        <v>0.01039022083888277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SUGARINCOFFEE</t>
+          <t>CHICKENSKINTYPE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Old</t>
+          <t>Middle</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>-63222351.83978494</v>
+        <v>-0.2248227010661035</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006899403230645175</v>
+        <v>0.04655267345822717</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SUGARINTEA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.2510229955485136</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.004169331168111846</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SUGARINCOFFEE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Old</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3069742096387921</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0006903757059677797</v>
       </c>
     </row>
   </sheetData>
